--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\soft\cv_vibrometry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD0C918-9B7E-436C-AD6D-118EAB85B10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DB003B-75A9-4EB2-A2F1-9471524510EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C33BA12C-13D2-45F4-B160-36382B4637A6}"/>
   </bookViews>
@@ -327,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -351,9 +351,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
@@ -853,9 +850,9 @@
       <c r="D3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -890,26 +887,26 @@
       <c r="D4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
@@ -927,26 +924,26 @@
       <c r="D5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
@@ -964,26 +961,26 @@
       <c r="D6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
@@ -1001,26 +998,26 @@
       <c r="D7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
       <c r="K7" s="5"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
@@ -1038,13 +1035,13 @@
       <c r="D8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
@@ -1052,12 +1049,12 @@
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
@@ -1075,26 +1072,26 @@
       <c r="D9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
@@ -1112,26 +1109,26 @@
       <c r="D10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
@@ -1149,26 +1146,26 @@
       <c r="D11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
       <c r="R11" s="5"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
@@ -1186,26 +1183,26 @@
       <c r="D12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
@@ -1223,26 +1220,26 @@
       <c r="D13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
-      <c r="X13" s="9"/>
+      <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
@@ -1260,26 +1257,26 @@
       <c r="D14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
-      <c r="U14" s="9"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
-      <c r="X14" s="9"/>
+      <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
@@ -1297,26 +1294,26 @@
       <c r="D15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="9"/>
-      <c r="S15" s="9"/>
-      <c r="T15" s="9"/>
-      <c r="U15" s="15"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="14"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
-      <c r="X15" s="9"/>
+      <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
@@ -1334,26 +1331,26 @@
       <c r="D16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="9"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="9"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
       <c r="U16" s="5"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-      <c r="X16" s="9"/>
+      <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
@@ -1371,26 +1368,26 @@
       <c r="D17" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="9"/>
-      <c r="U17" s="9"/>
-      <c r="V17" s="9"/>
-      <c r="W17" s="9"/>
-      <c r="X17" s="9"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="3"/>
+      <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
@@ -1411,21 +1408,21 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="15"/>
-      <c r="S18" s="15"/>
-      <c r="T18" s="15"/>
-      <c r="U18" s="15"/>
-      <c r="V18" s="15"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="14"/>
+      <c r="V18" s="14"/>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
@@ -1461,8 +1458,8 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-      <c r="U19" s="14"/>
-      <c r="V19" s="14"/>
+      <c r="U19" s="13"/>
+      <c r="V19" s="13"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
